--- a/mosip_master/xlsx/blocklisted_words.xlsx
+++ b/mosip_master/xlsx/blocklisted_words.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gokulraj\Documents\GitHub\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\mosip-data-1.3.0\mosip-data-1.3.0\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9628C418-2204-4629-931A-AD15AC08E158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3085E28D-FFBA-44E4-AB83-C5D9B48471D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
   <si>
     <t>lang_code</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>Blocklisted Word</t>
+  </si>
+  <si>
+    <t>sin</t>
+  </si>
+  <si>
+    <t>අවහිර කළ වචනය</t>
   </si>
 </sst>
 </file>
@@ -469,16 +475,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -492,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -506,7 +512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -520,7 +526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -534,7 +540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -548,7 +554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -562,7 +568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -576,8 +582,50 @@
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mosip_master/xlsx/blocklisted_words.xlsx
+++ b/mosip_master/xlsx/blocklisted_words.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\mosip-data-1.3.0\mosip-data-1.3.0\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\sludi-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3085E28D-FFBA-44E4-AB83-C5D9B48471D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA562D8-DA6A-4DC6-B6EA-BBEDD55B9144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>lang_code</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>අවහිර කළ වචනය</t>
+  </si>
+  <si>
+    <t>asfgd</t>
+  </si>
+  <si>
+    <t>vbgd</t>
+  </si>
+  <si>
+    <t>rjkiuy</t>
   </si>
 </sst>
 </file>
@@ -587,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -601,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
@@ -615,7 +624,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
